--- a/public/exports-from-60/29189366.xlsx
+++ b/public/exports-from-60/29189366.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220432</t>
+          <t xml:space="preserve">311220436</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809064</t>
+          <t xml:space="preserve">311809066</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809060</t>
+          <t xml:space="preserve">311809066</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809061</t>
+          <t xml:space="preserve">311809066</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">

--- a/public/exports-from-60/29189366.xlsx
+++ b/public/exports-from-60/29189366.xlsx
@@ -4414,7 +4414,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220436</t>
+          <t xml:space="preserve">311220432</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221033</t>
+          <t xml:space="preserve">311221046</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809064</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">

--- a/public/exports-from-60/29189366.xlsx
+++ b/public/exports-from-60/29189366.xlsx
@@ -5689,7 +5689,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221046</t>
+          <t xml:space="preserve">311221033</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809060</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809061</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
